--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -18473,6 +18473,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B788" t="n">
+        <v>12789</v>
+      </c>
+      <c r="C788" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="D788" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="E788" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="F788" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="G788" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -18496,6 +18496,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B789" t="n">
+        <v>13256</v>
+      </c>
+      <c r="C789" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D789" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="E789" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="F789" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="G789" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -18504,7 +18504,7 @@
         <v>13256</v>
       </c>
       <c r="C789" t="n">
-        <v>2.75</v>
+        <v>2.76999998092651</v>
       </c>
       <c r="D789" t="n">
         <v>2.69000005722046</v>
@@ -18516,6 +18516,29 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G789" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B790" t="n">
+        <v>5316</v>
+      </c>
+      <c r="C790" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="D790" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E790" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F790" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="G790" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -18542,6 +18542,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B791" t="n">
+        <v>27935</v>
+      </c>
+      <c r="C791" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D791" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E791" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="F791" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="G791" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -18383,22 +18383,22 @@
     </row>
     <row r="784">
       <c r="A784" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B784" t="n">
-        <v>975</v>
+        <v>7318</v>
       </c>
       <c r="C784" t="n">
-        <v>2.85999989509583</v>
+        <v>2.86999988555908</v>
       </c>
       <c r="D784" t="n">
-        <v>2.84999990463257</v>
+        <v>2.80999994277954</v>
       </c>
       <c r="E784" t="n">
         <v>2.84999990463257</v>
       </c>
       <c r="F784" t="n">
-        <v>2.85999989509583</v>
+        <v>2.8199999332428</v>
       </c>
       <c r="G784" t="s">
         <v>7</v>
@@ -18406,22 +18406,22 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B785" t="n">
-        <v>53709</v>
+        <v>975</v>
       </c>
       <c r="C785" t="n">
-        <v>2.83999991416931</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="D785" t="n">
-        <v>2.51999998092651</v>
+        <v>2.84999990463257</v>
       </c>
       <c r="E785" t="n">
-        <v>2.79999995231628</v>
+        <v>2.84999990463257</v>
       </c>
       <c r="F785" t="n">
-        <v>2.78999996185303</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="G785" t="s">
         <v>7</v>
@@ -18429,22 +18429,22 @@
     </row>
     <row r="786">
       <c r="A786" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B786" t="n">
-        <v>14418</v>
+        <v>53709</v>
       </c>
       <c r="C786" t="n">
-        <v>2.73000001907349</v>
+        <v>2.83999991416931</v>
       </c>
       <c r="D786" t="n">
-        <v>2.67000007629395</v>
+        <v>2.51999998092651</v>
       </c>
       <c r="E786" t="n">
-        <v>2.72000002861023</v>
+        <v>2.79999995231628</v>
       </c>
       <c r="F786" t="n">
-        <v>2.73000001907349</v>
+        <v>2.78999996185303</v>
       </c>
       <c r="G786" t="s">
         <v>7</v>
@@ -18452,22 +18452,22 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B787" t="n">
-        <v>6467</v>
+        <v>14418</v>
       </c>
       <c r="C787" t="n">
-        <v>2.90000009536743</v>
+        <v>2.73000001907349</v>
       </c>
       <c r="D787" t="n">
-        <v>2.69000005722046</v>
+        <v>2.67000007629395</v>
       </c>
       <c r="E787" t="n">
-        <v>2.75999999046326</v>
+        <v>2.72000002861023</v>
       </c>
       <c r="F787" t="n">
-        <v>2.80999994277954</v>
+        <v>2.73000001907349</v>
       </c>
       <c r="G787" t="s">
         <v>7</v>
@@ -18475,22 +18475,22 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B788" t="n">
-        <v>12789</v>
+        <v>6467</v>
       </c>
       <c r="C788" t="n">
-        <v>2.80999994277954</v>
+        <v>2.90000009536743</v>
       </c>
       <c r="D788" t="n">
-        <v>2.70000004768372</v>
+        <v>2.69000005722046</v>
       </c>
       <c r="E788" t="n">
         <v>2.75999999046326</v>
       </c>
       <c r="F788" t="n">
-        <v>2.79999995231628</v>
+        <v>2.80999994277954</v>
       </c>
       <c r="G788" t="s">
         <v>7</v>
@@ -18498,22 +18498,22 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B789" t="n">
-        <v>13256</v>
+        <v>12789</v>
       </c>
       <c r="C789" t="n">
-        <v>2.76999998092651</v>
+        <v>2.80999994277954</v>
       </c>
       <c r="D789" t="n">
-        <v>2.69000005722046</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="E789" t="n">
-        <v>2.73000001907349</v>
+        <v>2.75999999046326</v>
       </c>
       <c r="F789" t="n">
-        <v>2.76999998092651</v>
+        <v>2.79999995231628</v>
       </c>
       <c r="G789" t="s">
         <v>7</v>
@@ -18521,22 +18521,22 @@
     </row>
     <row r="790">
       <c r="A790" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B790" t="n">
-        <v>5316</v>
+        <v>13256</v>
       </c>
       <c r="C790" t="n">
-        <v>2.75999999046326</v>
+        <v>2.76999998092651</v>
       </c>
       <c r="D790" t="n">
-        <v>2.66000008583069</v>
+        <v>2.69000005722046</v>
       </c>
       <c r="E790" t="n">
-        <v>2.70000004768372</v>
+        <v>2.73000001907349</v>
       </c>
       <c r="F790" t="n">
-        <v>2.75999999046326</v>
+        <v>2.76999998092651</v>
       </c>
       <c r="G790" t="s">
         <v>7</v>
@@ -18544,24 +18544,47 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B791" t="n">
-        <v>27935</v>
+        <v>5316</v>
       </c>
       <c r="C791" t="n">
-        <v>2.78999996185303</v>
+        <v>2.75999999046326</v>
       </c>
       <c r="D791" t="n">
         <v>2.66000008583069</v>
       </c>
       <c r="E791" t="n">
-        <v>2.78999996185303</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="F791" t="n">
-        <v>2.72000002861023</v>
+        <v>2.75999999046326</v>
       </c>
       <c r="G791" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B792" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C792" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D792" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="E792" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F792" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G792" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -21019,6 +21019,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B795" t="n">
+        <v>196842</v>
+      </c>
+      <c r="C795" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="D795" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="E795" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="F795" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="G795" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="H795" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -21045,6 +21045,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B796" t="n">
+        <v>320792</v>
+      </c>
+      <c r="C796" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="D796" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E796" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="F796" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="G796" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="H796" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2" t="n">
-        <v>8.90654182434082</v>
+        <v>8.90654277801514</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G8" t="n">
-        <v>8.34813785552979</v>
+        <v>8.3481388092041</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>8.32952499389648</v>
+        <v>8.32952404022217</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G10" t="n">
-        <v>8.44120597839355</v>
+        <v>8.44120502471924</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G14" t="n">
-        <v>8.46912574768066</v>
+        <v>8.46912670135498</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.49400043487549</v>
       </c>
       <c r="G23" t="n">
-        <v>7.90513849258423</v>
+        <v>7.90513801574707</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G25" t="n">
-        <v>7.34301137924194</v>
+        <v>7.34301090240479</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>7.06380987167358</v>
+        <v>7.06380939483643</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>7.25</v>
       </c>
       <c r="G28" t="n">
-        <v>6.74738025665283</v>
+        <v>6.74738073348999</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>7.15222358703613</v>
+        <v>7.15222311019897</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G46" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G61" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G64" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>6</v>
       </c>
       <c r="G65" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>5.91908168792725</v>
+        <v>5.91908121109009</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>6.49609851837158</v>
+        <v>6.49609899520874</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42164516448975</v>
+        <v>6.42164468765259</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>6.32857751846313</v>
+        <v>6.32857799530029</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>6.42164516448975</v>
+        <v>6.42164468765259</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G89" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>5.97492218017578</v>
+        <v>5.97492170333862</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>5.97492218017578</v>
+        <v>5.97492170333862</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>5.99353504180908</v>
+        <v>5.99353551864624</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G107" t="n">
-        <v>5.91908168792725</v>
+        <v>5.91908121109009</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G115" t="n">
-        <v>5.80740070343018</v>
+        <v>5.80740022659302</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6</v>
       </c>
       <c r="G128" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>5.47235870361328</v>
+        <v>5.47235822677612</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>4.65336561203003</v>
+        <v>4.65336608886719</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>4.82088661193848</v>
+        <v>4.82088708877563</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.48584461212158</v>
+        <v>4.48584508895874</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>4.23456287384033</v>
+        <v>4.23456335067749</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>5.41651821136475</v>
+        <v>5.41651773452759</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>5.47235870361328</v>
+        <v>5.47235822677612</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G195" t="n">
-        <v>5.41651821136475</v>
+        <v>5.41651773452759</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -21068,6 +21068,32 @@
         <v>3.34999990463257</v>
       </c>
       <c r="H796" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B797" t="n">
+        <v>120641</v>
+      </c>
+      <c r="C797" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="D797" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E797" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="F797" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="G797" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="H797" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2" t="n">
-        <v>8.90654277801514</v>
+        <v>8.90654182434082</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G8" t="n">
-        <v>8.3481388092041</v>
+        <v>8.34813785552979</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>8.32952404022217</v>
+        <v>8.32952499389648</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G10" t="n">
-        <v>8.44120502471924</v>
+        <v>8.44120597839355</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G14" t="n">
-        <v>8.46912670135498</v>
+        <v>8.46912574768066</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.49400043487549</v>
       </c>
       <c r="G23" t="n">
-        <v>7.90513801574707</v>
+        <v>7.90513849258423</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G25" t="n">
-        <v>7.34301090240479</v>
+        <v>7.34301137924194</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>7.06380939483643</v>
+        <v>7.06380987167358</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>7.25</v>
       </c>
       <c r="G28" t="n">
-        <v>6.74738073348999</v>
+        <v>6.74738025665283</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>7.15222311019897</v>
+        <v>7.15222358703613</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>6.08660221099854</v>
+        <v>6.08660268783569</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G46" t="n">
-        <v>6.16105651855469</v>
+        <v>6.16105604171753</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G61" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G64" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>6</v>
       </c>
       <c r="G65" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>5.63987922668457</v>
+        <v>5.63987970352173</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>5.91908121109009</v>
+        <v>5.91908168792725</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>6.49609899520874</v>
+        <v>6.49609851837158</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42164468765259</v>
+        <v>6.42164516448975</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>6.32857799530029</v>
+        <v>6.32857751846313</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>6.42164468765259</v>
+        <v>6.42164516448975</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G89" t="n">
-        <v>6.16105651855469</v>
+        <v>6.16105604171753</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>6.16105651855469</v>
+        <v>6.16105604171753</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>5.97492170333862</v>
+        <v>5.97492218017578</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>5.97492170333862</v>
+        <v>5.97492218017578</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>5.99353551864624</v>
+        <v>5.99353504180908</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>6.08660221099854</v>
+        <v>6.08660268783569</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G107" t="n">
-        <v>5.91908121109009</v>
+        <v>5.91908168792725</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>6.08660221099854</v>
+        <v>6.08660268783569</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G115" t="n">
-        <v>5.80740022659302</v>
+        <v>5.80740070343018</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.63987922668457</v>
+        <v>5.63987970352173</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>5.63987922668457</v>
+        <v>5.63987970352173</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6</v>
       </c>
       <c r="G128" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>5.47235822677612</v>
+        <v>5.47235870361328</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>4.65336608886719</v>
+        <v>4.65336561203003</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>4.82088708877563</v>
+        <v>4.82088661193848</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.48584508895874</v>
+        <v>4.48584461212158</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>4.23456335067749</v>
+        <v>4.23456287384033</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>5.41651773452759</v>
+        <v>5.41651821136475</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.30483675003052</v>
+        <v>5.30483722686768</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.30483675003052</v>
+        <v>5.30483722686768</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>5.30483675003052</v>
+        <v>5.30483722686768</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>5.47235822677612</v>
+        <v>5.47235870361328</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G195" t="n">
-        <v>5.41651773452759</v>
+        <v>5.41651821136475</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -21094,6 +21094,32 @@
         <v>3.09999990463257</v>
       </c>
       <c r="H797" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B798" t="n">
+        <v>65387</v>
+      </c>
+      <c r="C798" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="D798" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="E798" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="F798" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="G798" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="H798" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -21175,6 +21175,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="801">
+      <c r="A801" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B801" t="n">
+        <v>5674</v>
+      </c>
+      <c r="C801" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D801" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="E801" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="F801" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="G801" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="H801" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -18857,8 +18857,31 @@
       <c r="E804" t="n">
         <v>3.35999989509583</v>
       </c>
-      <c r="F804"/>
+      <c r="F804" t="n">
+        <v>3.35999989509583</v>
+      </c>
       <c r="G804" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B805" t="n">
+        <v>154993</v>
+      </c>
+      <c r="C805" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D805" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="E805" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="F805"/>
+      <c r="G805" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -18880,8 +18880,31 @@
       <c r="E805" t="n">
         <v>3.42000007629395</v>
       </c>
-      <c r="F805"/>
+      <c r="F805" t="n">
+        <v>3.63000011444092</v>
+      </c>
       <c r="G805" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B806" t="n">
+        <v>17256</v>
+      </c>
+      <c r="C806" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D806" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="E806" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F806"/>
+      <c r="G806" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -18903,8 +18903,31 @@
       <c r="E806" t="n">
         <v>3.64000010490417</v>
       </c>
-      <c r="F806"/>
+      <c r="F806" t="n">
+        <v>3.52999997138977</v>
+      </c>
       <c r="G806" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B807" t="n">
+        <v>27477</v>
+      </c>
+      <c r="C807" t="n">
+        <v>3.67000007629395</v>
+      </c>
+      <c r="D807" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="E807" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="F807"/>
+      <c r="G807" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -18926,8 +18926,31 @@
       <c r="E807" t="n">
         <v>3.50999999046326</v>
       </c>
-      <c r="F807"/>
+      <c r="F807" t="n">
+        <v>3.67000007629395</v>
+      </c>
       <c r="G807" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B808" t="n">
+        <v>43022</v>
+      </c>
+      <c r="C808" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="D808" t="n">
+        <v>3.54999995231628</v>
+      </c>
+      <c r="E808" t="n">
+        <v>3.67000007629395</v>
+      </c>
+      <c r="F808"/>
+      <c r="G808" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -18956,6 +18956,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B809" t="n">
+        <v>13640</v>
+      </c>
+      <c r="C809" t="n">
+        <v>3.67000007629395</v>
+      </c>
+      <c r="D809" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="E809" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="F809" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G809" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2" t="n">
-        <v>8.90654182434082</v>
+        <v>8.90654277801514</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G8" t="n">
-        <v>8.34813785552979</v>
+        <v>8.3481388092041</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>8.32952499389648</v>
+        <v>8.32952404022217</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G10" t="n">
-        <v>8.44120597839355</v>
+        <v>8.44120502471924</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G14" t="n">
-        <v>8.46912574768066</v>
+        <v>8.46912670135498</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.49400043487549</v>
       </c>
       <c r="G23" t="n">
-        <v>7.90513849258423</v>
+        <v>7.90513801574707</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G25" t="n">
-        <v>7.34301137924194</v>
+        <v>7.34301090240479</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>7.06380987167358</v>
+        <v>7.06380939483643</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>7.25</v>
       </c>
       <c r="G28" t="n">
-        <v>6.74738025665283</v>
+        <v>6.74738073348999</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>7.15222358703613</v>
+        <v>7.15222311019897</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G46" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G61" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G64" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>6</v>
       </c>
       <c r="G65" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>5.91908168792725</v>
+        <v>5.91908121109009</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>6.49609851837158</v>
+        <v>6.49609899520874</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42164516448975</v>
+        <v>6.42164468765259</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>6.32857751846313</v>
+        <v>6.32857799530029</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>6.42164516448975</v>
+        <v>6.42164468765259</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G89" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>5.97492218017578</v>
+        <v>5.97492170333862</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>5.97492218017578</v>
+        <v>5.97492170333862</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>5.99353504180908</v>
+        <v>5.99353551864624</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G107" t="n">
-        <v>5.91908168792725</v>
+        <v>5.91908121109009</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G115" t="n">
-        <v>5.80740070343018</v>
+        <v>5.80740022659302</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6</v>
       </c>
       <c r="G128" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>5.47235870361328</v>
+        <v>5.47235822677612</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>4.65336561203003</v>
+        <v>4.65336608886719</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>4.82088661193848</v>
+        <v>4.82088708877563</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.48584461212158</v>
+        <v>4.48584508895874</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>4.23456287384033</v>
+        <v>4.23456335067749</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>5.41651821136475</v>
+        <v>5.41651773452759</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>5.47235870361328</v>
+        <v>5.47235822677612</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G195" t="n">
-        <v>5.41651821136475</v>
+        <v>5.41651773452759</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -21458,6 +21458,32 @@
         <v>3.46000003814697</v>
       </c>
       <c r="H811" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B812" t="n">
+        <v>6342</v>
+      </c>
+      <c r="C812" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="D812" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="E812" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="F812" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="G812" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="H812" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2" t="n">
-        <v>8.90654277801514</v>
+        <v>8.90654182434082</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G8" t="n">
-        <v>8.3481388092041</v>
+        <v>8.34813785552979</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>8.32952404022217</v>
+        <v>8.32952499389648</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G10" t="n">
-        <v>8.44120502471924</v>
+        <v>8.44120597839355</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G14" t="n">
-        <v>8.46912670135498</v>
+        <v>8.46912574768066</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.49400043487549</v>
       </c>
       <c r="G23" t="n">
-        <v>7.90513801574707</v>
+        <v>7.90513849258423</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G25" t="n">
-        <v>7.34301090240479</v>
+        <v>7.34301137924194</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>7.06380939483643</v>
+        <v>7.06380987167358</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>7.25</v>
       </c>
       <c r="G28" t="n">
-        <v>6.74738073348999</v>
+        <v>6.74738025665283</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>7.15222311019897</v>
+        <v>7.15222358703613</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>6.08660221099854</v>
+        <v>6.08660268783569</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G46" t="n">
-        <v>6.16105651855469</v>
+        <v>6.16105604171753</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G61" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G64" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>6</v>
       </c>
       <c r="G65" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>5.63987922668457</v>
+        <v>5.63987970352173</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>5.91908121109009</v>
+        <v>5.91908168792725</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>6.49609899520874</v>
+        <v>6.49609851837158</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42164468765259</v>
+        <v>6.42164516448975</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>6.32857799530029</v>
+        <v>6.32857751846313</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>6.42164468765259</v>
+        <v>6.42164516448975</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G89" t="n">
-        <v>6.16105651855469</v>
+        <v>6.16105604171753</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>6.16105651855469</v>
+        <v>6.16105604171753</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>5.97492170333862</v>
+        <v>5.97492218017578</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>5.97492170333862</v>
+        <v>5.97492218017578</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>5.99353551864624</v>
+        <v>5.99353504180908</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>6.08660221099854</v>
+        <v>6.08660268783569</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G107" t="n">
-        <v>5.91908121109009</v>
+        <v>5.91908168792725</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>6.08660221099854</v>
+        <v>6.08660268783569</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G115" t="n">
-        <v>5.80740022659302</v>
+        <v>5.80740070343018</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.63987922668457</v>
+        <v>5.63987970352173</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>5.63987922668457</v>
+        <v>5.63987970352173</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6</v>
       </c>
       <c r="G128" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>5.47235822677612</v>
+        <v>5.47235870361328</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>4.65336608886719</v>
+        <v>4.65336561203003</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>4.82088708877563</v>
+        <v>4.82088661193848</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.48584508895874</v>
+        <v>4.48584461212158</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>4.23456335067749</v>
+        <v>4.23456287384033</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>5.41651773452759</v>
+        <v>5.41651821136475</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.30483675003052</v>
+        <v>5.30483722686768</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.30483675003052</v>
+        <v>5.30483722686768</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>5.30483675003052</v>
+        <v>5.30483722686768</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>5.47235822677612</v>
+        <v>5.47235870361328</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G195" t="n">
-        <v>5.41651773452759</v>
+        <v>5.41651821136475</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -21484,6 +21484,32 @@
         <v>3.44000005722046</v>
       </c>
       <c r="H812" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B813" t="n">
+        <v>12311</v>
+      </c>
+      <c r="C813" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="D813" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="E813" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="F813" t="n">
+        <v>3.26999998092651</v>
+      </c>
+      <c r="G813" t="n">
+        <v>3.26999998092651</v>
+      </c>
+      <c r="H813" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -23955,6 +23955,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="814">
+      <c r="A814" t="s">
+        <v>9</v>
+      </c>
+      <c r="B814" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C814" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="D814" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="E814" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F814" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G814" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H814" t="n">
+        <v>8261</v>
+      </c>
+      <c r="I814" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="s">
+        <v>9</v>
+      </c>
+      <c r="B815" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C815" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D815" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="E815" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F815" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="G815" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="H815" t="n">
+        <v>2673</v>
+      </c>
+      <c r="I815" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -23995,7 +23995,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="D815" t="n">
-        <v>3.29999995231628</v>
+        <v>3.3199999332428</v>
       </c>
       <c r="E815" t="n">
         <v>3.25</v>
@@ -24010,6 +24010,35 @@
         <v>2673</v>
       </c>
       <c r="I815" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="s">
+        <v>9</v>
+      </c>
+      <c r="B816" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C816" t="n">
+        <v>3.33999991416931</v>
+      </c>
+      <c r="D816" t="n">
+        <v>3.33999991416931</v>
+      </c>
+      <c r="E816" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F816" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="G816" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="H816" t="n">
+        <v>2550</v>
+      </c>
+      <c r="I816" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2" t="n">
-        <v>8.90654182434082</v>
+        <v>8.90654277801514</v>
       </c>
       <c r="H2" t="n">
         <v>21006</v>
@@ -601,7 +601,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G8" t="n">
-        <v>8.34813785552979</v>
+        <v>8.3481388092041</v>
       </c>
       <c r="H8" t="n">
         <v>22641</v>
@@ -630,7 +630,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>8.32952499389648</v>
+        <v>8.32952404022217</v>
       </c>
       <c r="H9" t="n">
         <v>1181</v>
@@ -659,7 +659,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G10" t="n">
-        <v>8.44120597839355</v>
+        <v>8.44120502471924</v>
       </c>
       <c r="H10" t="n">
         <v>9608</v>
@@ -775,7 +775,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G14" t="n">
-        <v>8.46912574768066</v>
+        <v>8.46912670135498</v>
       </c>
       <c r="H14" t="n">
         <v>19218</v>
@@ -1036,7 +1036,7 @@
         <v>8.49400043487549</v>
       </c>
       <c r="G23" t="n">
-        <v>7.90513849258423</v>
+        <v>7.90513801574707</v>
       </c>
       <c r="H23" t="n">
         <v>9784</v>
@@ -1094,7 +1094,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G25" t="n">
-        <v>7.34301137924194</v>
+        <v>7.34301090240479</v>
       </c>
       <c r="H25" t="n">
         <v>40060</v>
@@ -1123,7 +1123,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>7.06380987167358</v>
+        <v>7.06380939483643</v>
       </c>
       <c r="H26" t="n">
         <v>27229</v>
@@ -1181,7 +1181,7 @@
         <v>7.25</v>
       </c>
       <c r="G28" t="n">
-        <v>6.74738025665283</v>
+        <v>6.74738073348999</v>
       </c>
       <c r="H28" t="n">
         <v>1323</v>
@@ -1268,7 +1268,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>7.15222358703613</v>
+        <v>7.15222311019897</v>
       </c>
       <c r="H31" t="n">
         <v>2726</v>
@@ -1500,7 +1500,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H39" t="n">
         <v>2121</v>
@@ -1587,7 +1587,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H42" t="n">
         <v>14886</v>
@@ -1674,7 +1674,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H45" t="n">
         <v>3200</v>
@@ -1703,7 +1703,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G46" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H46" t="n">
         <v>7590</v>
@@ -2051,7 +2051,7 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H58" t="n">
         <v>16192</v>
@@ -2080,7 +2080,7 @@
         <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H59" t="n">
         <v>15022</v>
@@ -2109,7 +2109,7 @@
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H60" t="n">
         <v>6500</v>
@@ -2138,7 +2138,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G61" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H61" t="n">
         <v>9991</v>
@@ -2167,7 +2167,7 @@
         <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H62" t="n">
         <v>5983</v>
@@ -2196,7 +2196,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H63" t="n">
         <v>2350</v>
@@ -2225,7 +2225,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G64" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H64" t="n">
         <v>12550</v>
@@ -2254,7 +2254,7 @@
         <v>6</v>
       </c>
       <c r="G65" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H65" t="n">
         <v>711</v>
@@ -2312,7 +2312,7 @@
         <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H67" t="n">
         <v>6042</v>
@@ -2457,7 +2457,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H72" t="n">
         <v>4949</v>
@@ -2515,7 +2515,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>5.91908168792725</v>
+        <v>5.91908121109009</v>
       </c>
       <c r="H74" t="n">
         <v>7919</v>
@@ -2544,7 +2544,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>6.49609851837158</v>
+        <v>6.49609899520874</v>
       </c>
       <c r="H75" t="n">
         <v>22221</v>
@@ -2602,7 +2602,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42164516448975</v>
+        <v>6.42164468765259</v>
       </c>
       <c r="H77" t="n">
         <v>10996</v>
@@ -2631,7 +2631,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>6.32857751846313</v>
+        <v>6.32857799530029</v>
       </c>
       <c r="H78" t="n">
         <v>6843</v>
@@ -2718,7 +2718,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>6.42164516448975</v>
+        <v>6.42164468765259</v>
       </c>
       <c r="H81" t="n">
         <v>10110</v>
@@ -2950,7 +2950,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G89" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H89" t="n">
         <v>3529</v>
@@ -2979,7 +2979,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H90" t="n">
         <v>250</v>
@@ -3095,7 +3095,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>5.97492218017578</v>
+        <v>5.97492170333862</v>
       </c>
       <c r="H94" t="n">
         <v>3556</v>
@@ -3124,7 +3124,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>5.97492218017578</v>
+        <v>5.97492170333862</v>
       </c>
       <c r="H95" t="n">
         <v>3100</v>
@@ -3211,7 +3211,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H98" t="n">
         <v>1510</v>
@@ -3327,7 +3327,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>5.99353504180908</v>
+        <v>5.99353551864624</v>
       </c>
       <c r="H102" t="n">
         <v>2571</v>
@@ -3385,7 +3385,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H104" t="n">
         <v>400</v>
@@ -3414,7 +3414,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H105" t="n">
         <v>11078</v>
@@ -3472,7 +3472,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G107" t="n">
-        <v>5.91908168792725</v>
+        <v>5.91908121109009</v>
       </c>
       <c r="H107" t="n">
         <v>3427</v>
@@ -3501,7 +3501,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H108" t="n">
         <v>100</v>
@@ -3704,7 +3704,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G115" t="n">
-        <v>5.80740070343018</v>
+        <v>5.80740022659302</v>
       </c>
       <c r="H115" t="n">
         <v>5460</v>
@@ -3878,7 +3878,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H121" t="n">
         <v>2301</v>
@@ -3936,7 +3936,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H123" t="n">
         <v>17070</v>
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H124" t="n">
         <v>2313</v>
@@ -4052,7 +4052,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H127" t="n">
         <v>3066</v>
@@ -4081,7 +4081,7 @@
         <v>6</v>
       </c>
       <c r="G128" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H128" t="n">
         <v>3659</v>
@@ -4139,7 +4139,7 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H130" t="n">
         <v>6752</v>
@@ -4197,7 +4197,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>5.47235870361328</v>
+        <v>5.47235822677612</v>
       </c>
       <c r="H132" t="n">
         <v>1269</v>
@@ -4487,7 +4487,7 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>4.65336561203003</v>
+        <v>4.65336608886719</v>
       </c>
       <c r="H142" t="n">
         <v>9029</v>
@@ -4719,7 +4719,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>4.82088661193848</v>
+        <v>4.82088708877563</v>
       </c>
       <c r="H150" t="n">
         <v>11386</v>
@@ -4951,7 +4951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.48584461212158</v>
+        <v>4.48584508895874</v>
       </c>
       <c r="H158" t="n">
         <v>12780</v>
@@ -5038,7 +5038,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>4.23456287384033</v>
+        <v>4.23456335067749</v>
       </c>
       <c r="H161" t="n">
         <v>9290</v>
@@ -5444,7 +5444,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>5.41651821136475</v>
+        <v>5.41651773452759</v>
       </c>
       <c r="H175" t="n">
         <v>5482</v>
@@ -5531,7 +5531,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H178" t="n">
         <v>3026</v>
@@ -5560,7 +5560,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H180" t="n">
         <v>5941</v>
@@ -5879,7 +5879,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>5.47235870361328</v>
+        <v>5.47235822677612</v>
       </c>
       <c r="H190" t="n">
         <v>7694</v>
@@ -5908,7 +5908,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H191" t="n">
         <v>7118</v>
@@ -6024,7 +6024,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G195" t="n">
-        <v>5.41651821136475</v>
+        <v>5.41651773452759</v>
       </c>
       <c r="H195" t="n">
         <v>9390</v>
@@ -24039,6 +24039,64 @@
         <v>2550</v>
       </c>
       <c r="I816" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="s">
+        <v>9</v>
+      </c>
+      <c r="B817" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C817" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="D817" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="E817" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="F817" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="G817" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="H817" t="n">
+        <v>0</v>
+      </c>
+      <c r="I817" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="s">
+        <v>9</v>
+      </c>
+      <c r="B818" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C818" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="D818" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="E818" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="F818" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="G818" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="H818" t="n">
+        <v>8730</v>
+      </c>
+      <c r="I818" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -24082,7 +24082,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="D818" t="n">
-        <v>3.29999995231628</v>
+        <v>3.35999989509583</v>
       </c>
       <c r="E818" t="n">
         <v>3.28999996185303</v>
@@ -24097,6 +24097,35 @@
         <v>8730</v>
       </c>
       <c r="I818" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="s">
+        <v>9</v>
+      </c>
+      <c r="B819" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C819" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="D819" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="E819" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="F819" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="G819" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="H819" t="n">
+        <v>2420</v>
+      </c>
+      <c r="I819" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -24111,7 +24111,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="D819" t="n">
-        <v>3.32999992370605</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="E819" t="n">
         <v>3.32999992370605</v>
@@ -24126,6 +24126,35 @@
         <v>2420</v>
       </c>
       <c r="I819" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="s">
+        <v>9</v>
+      </c>
+      <c r="B820" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C820" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="D820" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="E820" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="F820" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="G820" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="H820" t="n">
+        <v>4056</v>
+      </c>
+      <c r="I820" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2" t="n">
-        <v>8.90654277801514</v>
+        <v>8.90654182434082</v>
       </c>
       <c r="H2" t="n">
         <v>21006</v>
@@ -601,7 +601,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G8" t="n">
-        <v>8.3481388092041</v>
+        <v>8.34813785552979</v>
       </c>
       <c r="H8" t="n">
         <v>22641</v>
@@ -630,7 +630,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>8.32952404022217</v>
+        <v>8.32952499389648</v>
       </c>
       <c r="H9" t="n">
         <v>1181</v>
@@ -659,7 +659,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G10" t="n">
-        <v>8.44120502471924</v>
+        <v>8.44120597839355</v>
       </c>
       <c r="H10" t="n">
         <v>9608</v>
@@ -775,7 +775,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G14" t="n">
-        <v>8.46912670135498</v>
+        <v>8.46912574768066</v>
       </c>
       <c r="H14" t="n">
         <v>19218</v>
@@ -1036,7 +1036,7 @@
         <v>8.49400043487549</v>
       </c>
       <c r="G23" t="n">
-        <v>7.90513801574707</v>
+        <v>7.90513849258423</v>
       </c>
       <c r="H23" t="n">
         <v>9784</v>
@@ -1094,7 +1094,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G25" t="n">
-        <v>7.34301090240479</v>
+        <v>7.34301137924194</v>
       </c>
       <c r="H25" t="n">
         <v>40060</v>
@@ -1123,7 +1123,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>7.06380939483643</v>
+        <v>7.06380987167358</v>
       </c>
       <c r="H26" t="n">
         <v>27229</v>
@@ -1181,7 +1181,7 @@
         <v>7.25</v>
       </c>
       <c r="G28" t="n">
-        <v>6.74738073348999</v>
+        <v>6.74738025665283</v>
       </c>
       <c r="H28" t="n">
         <v>1323</v>
@@ -1268,7 +1268,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>7.15222311019897</v>
+        <v>7.15222358703613</v>
       </c>
       <c r="H31" t="n">
         <v>2726</v>
@@ -1500,7 +1500,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H39" t="n">
         <v>2121</v>
@@ -1587,7 +1587,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>6.08660221099854</v>
+        <v>6.08660268783569</v>
       </c>
       <c r="H42" t="n">
         <v>14886</v>
@@ -1674,7 +1674,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H45" t="n">
         <v>3200</v>
@@ -1703,7 +1703,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G46" t="n">
-        <v>6.16105651855469</v>
+        <v>6.16105604171753</v>
       </c>
       <c r="H46" t="n">
         <v>7590</v>
@@ -2051,7 +2051,7 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H58" t="n">
         <v>16192</v>
@@ -2080,7 +2080,7 @@
         <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H59" t="n">
         <v>15022</v>
@@ -2109,7 +2109,7 @@
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H60" t="n">
         <v>6500</v>
@@ -2138,7 +2138,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G61" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H61" t="n">
         <v>9991</v>
@@ -2167,7 +2167,7 @@
         <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H62" t="n">
         <v>5983</v>
@@ -2196,7 +2196,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H63" t="n">
         <v>2350</v>
@@ -2225,7 +2225,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G64" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H64" t="n">
         <v>12550</v>
@@ -2254,7 +2254,7 @@
         <v>6</v>
       </c>
       <c r="G65" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H65" t="n">
         <v>711</v>
@@ -2312,7 +2312,7 @@
         <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H67" t="n">
         <v>6042</v>
@@ -2457,7 +2457,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>5.63987922668457</v>
+        <v>5.63987970352173</v>
       </c>
       <c r="H72" t="n">
         <v>4949</v>
@@ -2515,7 +2515,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>5.91908121109009</v>
+        <v>5.91908168792725</v>
       </c>
       <c r="H74" t="n">
         <v>7919</v>
@@ -2544,7 +2544,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>6.49609899520874</v>
+        <v>6.49609851837158</v>
       </c>
       <c r="H75" t="n">
         <v>22221</v>
@@ -2602,7 +2602,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42164468765259</v>
+        <v>6.42164516448975</v>
       </c>
       <c r="H77" t="n">
         <v>10996</v>
@@ -2631,7 +2631,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>6.32857799530029</v>
+        <v>6.32857751846313</v>
       </c>
       <c r="H78" t="n">
         <v>6843</v>
@@ -2718,7 +2718,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>6.42164468765259</v>
+        <v>6.42164516448975</v>
       </c>
       <c r="H81" t="n">
         <v>10110</v>
@@ -2950,7 +2950,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G89" t="n">
-        <v>6.16105651855469</v>
+        <v>6.16105604171753</v>
       </c>
       <c r="H89" t="n">
         <v>3529</v>
@@ -2979,7 +2979,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>6.16105651855469</v>
+        <v>6.16105604171753</v>
       </c>
       <c r="H90" t="n">
         <v>250</v>
@@ -3095,7 +3095,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>5.97492170333862</v>
+        <v>5.97492218017578</v>
       </c>
       <c r="H94" t="n">
         <v>3556</v>
@@ -3124,7 +3124,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>5.97492170333862</v>
+        <v>5.97492218017578</v>
       </c>
       <c r="H95" t="n">
         <v>3100</v>
@@ -3211,7 +3211,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H98" t="n">
         <v>1510</v>
@@ -3327,7 +3327,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>5.99353551864624</v>
+        <v>5.99353504180908</v>
       </c>
       <c r="H102" t="n">
         <v>2571</v>
@@ -3385,7 +3385,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>6.08660221099854</v>
+        <v>6.08660268783569</v>
       </c>
       <c r="H104" t="n">
         <v>400</v>
@@ -3414,7 +3414,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.14244270324707</v>
+        <v>6.14244318008423</v>
       </c>
       <c r="H105" t="n">
         <v>11078</v>
@@ -3472,7 +3472,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G107" t="n">
-        <v>5.91908121109009</v>
+        <v>5.91908168792725</v>
       </c>
       <c r="H107" t="n">
         <v>3427</v>
@@ -3501,7 +3501,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>6.08660221099854</v>
+        <v>6.08660268783569</v>
       </c>
       <c r="H108" t="n">
         <v>100</v>
@@ -3704,7 +3704,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G115" t="n">
-        <v>5.80740022659302</v>
+        <v>5.80740070343018</v>
       </c>
       <c r="H115" t="n">
         <v>5460</v>
@@ -3878,7 +3878,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.63987922668457</v>
+        <v>5.63987970352173</v>
       </c>
       <c r="H121" t="n">
         <v>2301</v>
@@ -3936,7 +3936,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>5.63987922668457</v>
+        <v>5.63987970352173</v>
       </c>
       <c r="H123" t="n">
         <v>17070</v>
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H124" t="n">
         <v>2313</v>
@@ -4052,7 +4052,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H127" t="n">
         <v>3066</v>
@@ -4081,7 +4081,7 @@
         <v>6</v>
       </c>
       <c r="G128" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H128" t="n">
         <v>3659</v>
@@ -4139,7 +4139,7 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>5.58403873443604</v>
+        <v>5.58403921127319</v>
       </c>
       <c r="H130" t="n">
         <v>6752</v>
@@ -4197,7 +4197,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>5.47235822677612</v>
+        <v>5.47235870361328</v>
       </c>
       <c r="H132" t="n">
         <v>1269</v>
@@ -4487,7 +4487,7 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>4.65336608886719</v>
+        <v>4.65336561203003</v>
       </c>
       <c r="H142" t="n">
         <v>9029</v>
@@ -4719,7 +4719,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>4.82088708877563</v>
+        <v>4.82088661193848</v>
       </c>
       <c r="H150" t="n">
         <v>11386</v>
@@ -4951,7 +4951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.48584508895874</v>
+        <v>4.48584461212158</v>
       </c>
       <c r="H158" t="n">
         <v>12780</v>
@@ -5038,7 +5038,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>4.23456335067749</v>
+        <v>4.23456287384033</v>
       </c>
       <c r="H161" t="n">
         <v>9290</v>
@@ -5444,7 +5444,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>5.41651773452759</v>
+        <v>5.41651821136475</v>
       </c>
       <c r="H175" t="n">
         <v>5482</v>
@@ -5531,7 +5531,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.30483675003052</v>
+        <v>5.30483722686768</v>
       </c>
       <c r="H178" t="n">
         <v>3026</v>
@@ -5560,7 +5560,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.30483675003052</v>
+        <v>5.30483722686768</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>5.30483675003052</v>
+        <v>5.30483722686768</v>
       </c>
       <c r="H180" t="n">
         <v>5941</v>
@@ -5879,7 +5879,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>5.47235822677612</v>
+        <v>5.47235870361328</v>
       </c>
       <c r="H190" t="n">
         <v>7694</v>
@@ -5908,7 +5908,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>5.49097204208374</v>
+        <v>5.49097156524658</v>
       </c>
       <c r="H191" t="n">
         <v>7118</v>
@@ -6024,7 +6024,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G195" t="n">
-        <v>5.41651773452759</v>
+        <v>5.41651821136475</v>
       </c>
       <c r="H195" t="n">
         <v>9390</v>
@@ -24140,7 +24140,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="D820" t="n">
-        <v>3.39000010490417</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="E820" t="n">
         <v>3.32999992370605</v>
@@ -24155,6 +24155,35 @@
         <v>4056</v>
       </c>
       <c r="I820" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="s">
+        <v>9</v>
+      </c>
+      <c r="B821" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C821" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="D821" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="E821" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="F821" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="G821" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="H821" t="n">
+        <v>10513</v>
+      </c>
+      <c r="I821" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G2" t="n">
-        <v>8.90654182434082</v>
+        <v>8.90654277801514</v>
       </c>
       <c r="H2" t="n">
         <v>21006</v>
@@ -601,7 +601,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G8" t="n">
-        <v>8.34813785552979</v>
+        <v>8.3481388092041</v>
       </c>
       <c r="H8" t="n">
         <v>22641</v>
@@ -630,7 +630,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>8.32952499389648</v>
+        <v>8.32952404022217</v>
       </c>
       <c r="H9" t="n">
         <v>1181</v>
@@ -659,7 +659,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G10" t="n">
-        <v>8.44120597839355</v>
+        <v>8.44120502471924</v>
       </c>
       <c r="H10" t="n">
         <v>9608</v>
@@ -775,7 +775,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G14" t="n">
-        <v>8.46912574768066</v>
+        <v>8.46912670135498</v>
       </c>
       <c r="H14" t="n">
         <v>19218</v>
@@ -1036,7 +1036,7 @@
         <v>8.49400043487549</v>
       </c>
       <c r="G23" t="n">
-        <v>7.90513849258423</v>
+        <v>7.90513801574707</v>
       </c>
       <c r="H23" t="n">
         <v>9784</v>
@@ -1094,7 +1094,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G25" t="n">
-        <v>7.34301137924194</v>
+        <v>7.34301090240479</v>
       </c>
       <c r="H25" t="n">
         <v>40060</v>
@@ -1123,7 +1123,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>7.06380987167358</v>
+        <v>7.06380939483643</v>
       </c>
       <c r="H26" t="n">
         <v>27229</v>
@@ -1181,7 +1181,7 @@
         <v>7.25</v>
       </c>
       <c r="G28" t="n">
-        <v>6.74738025665283</v>
+        <v>6.74738073348999</v>
       </c>
       <c r="H28" t="n">
         <v>1323</v>
@@ -1268,7 +1268,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>7.15222358703613</v>
+        <v>7.15222311019897</v>
       </c>
       <c r="H31" t="n">
         <v>2726</v>
@@ -1500,7 +1500,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H39" t="n">
         <v>2121</v>
@@ -1587,7 +1587,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H42" t="n">
         <v>14886</v>
@@ -1674,7 +1674,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G45" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H45" t="n">
         <v>3200</v>
@@ -1703,7 +1703,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G46" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H46" t="n">
         <v>7590</v>
@@ -2051,7 +2051,7 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H58" t="n">
         <v>16192</v>
@@ -2080,7 +2080,7 @@
         <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H59" t="n">
         <v>15022</v>
@@ -2109,7 +2109,7 @@
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H60" t="n">
         <v>6500</v>
@@ -2138,7 +2138,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G61" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H61" t="n">
         <v>9991</v>
@@ -2167,7 +2167,7 @@
         <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H62" t="n">
         <v>5983</v>
@@ -2196,7 +2196,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H63" t="n">
         <v>2350</v>
@@ -2225,7 +2225,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G64" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H64" t="n">
         <v>12550</v>
@@ -2254,7 +2254,7 @@
         <v>6</v>
       </c>
       <c r="G65" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H65" t="n">
         <v>711</v>
@@ -2312,7 +2312,7 @@
         <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H67" t="n">
         <v>6042</v>
@@ -2457,7 +2457,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H72" t="n">
         <v>4949</v>
@@ -2515,7 +2515,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G74" t="n">
-        <v>5.91908168792725</v>
+        <v>5.91908121109009</v>
       </c>
       <c r="H74" t="n">
         <v>7919</v>
@@ -2544,7 +2544,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>6.49609851837158</v>
+        <v>6.49609899520874</v>
       </c>
       <c r="H75" t="n">
         <v>22221</v>
@@ -2602,7 +2602,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>6.42164516448975</v>
+        <v>6.42164468765259</v>
       </c>
       <c r="H77" t="n">
         <v>10996</v>
@@ -2631,7 +2631,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>6.32857751846313</v>
+        <v>6.32857799530029</v>
       </c>
       <c r="H78" t="n">
         <v>6843</v>
@@ -2718,7 +2718,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G81" t="n">
-        <v>6.42164516448975</v>
+        <v>6.42164468765259</v>
       </c>
       <c r="H81" t="n">
         <v>10110</v>
@@ -2950,7 +2950,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G89" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H89" t="n">
         <v>3529</v>
@@ -2979,7 +2979,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>6.16105604171753</v>
+        <v>6.16105651855469</v>
       </c>
       <c r="H90" t="n">
         <v>250</v>
@@ -3095,7 +3095,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>5.97492218017578</v>
+        <v>5.97492170333862</v>
       </c>
       <c r="H94" t="n">
         <v>3556</v>
@@ -3124,7 +3124,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>5.97492218017578</v>
+        <v>5.97492170333862</v>
       </c>
       <c r="H95" t="n">
         <v>3100</v>
@@ -3211,7 +3211,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H98" t="n">
         <v>1510</v>
@@ -3327,7 +3327,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>5.99353504180908</v>
+        <v>5.99353551864624</v>
       </c>
       <c r="H102" t="n">
         <v>2571</v>
@@ -3385,7 +3385,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H104" t="n">
         <v>400</v>
@@ -3414,7 +3414,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>6.14244318008423</v>
+        <v>6.14244270324707</v>
       </c>
       <c r="H105" t="n">
         <v>11078</v>
@@ -3472,7 +3472,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G107" t="n">
-        <v>5.91908168792725</v>
+        <v>5.91908121109009</v>
       </c>
       <c r="H107" t="n">
         <v>3427</v>
@@ -3501,7 +3501,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>6.08660268783569</v>
+        <v>6.08660221099854</v>
       </c>
       <c r="H108" t="n">
         <v>100</v>
@@ -3704,7 +3704,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G115" t="n">
-        <v>5.80740070343018</v>
+        <v>5.80740022659302</v>
       </c>
       <c r="H115" t="n">
         <v>5460</v>
@@ -3878,7 +3878,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H121" t="n">
         <v>2301</v>
@@ -3936,7 +3936,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>5.63987970352173</v>
+        <v>5.63987922668457</v>
       </c>
       <c r="H123" t="n">
         <v>17070</v>
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H124" t="n">
         <v>2313</v>
@@ -4052,7 +4052,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H127" t="n">
         <v>3066</v>
@@ -4081,7 +4081,7 @@
         <v>6</v>
       </c>
       <c r="G128" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H128" t="n">
         <v>3659</v>
@@ -4139,7 +4139,7 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>5.58403921127319</v>
+        <v>5.58403873443604</v>
       </c>
       <c r="H130" t="n">
         <v>6752</v>
@@ -4197,7 +4197,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G132" t="n">
-        <v>5.47235870361328</v>
+        <v>5.47235822677612</v>
       </c>
       <c r="H132" t="n">
         <v>1269</v>
@@ -4487,7 +4487,7 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>4.65336561203003</v>
+        <v>4.65336608886719</v>
       </c>
       <c r="H142" t="n">
         <v>9029</v>
@@ -4719,7 +4719,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>4.82088661193848</v>
+        <v>4.82088708877563</v>
       </c>
       <c r="H150" t="n">
         <v>11386</v>
@@ -4951,7 +4951,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G158" t="n">
-        <v>4.48584461212158</v>
+        <v>4.48584508895874</v>
       </c>
       <c r="H158" t="n">
         <v>12780</v>
@@ -5038,7 +5038,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>4.23456287384033</v>
+        <v>4.23456335067749</v>
       </c>
       <c r="H161" t="n">
         <v>9290</v>
@@ -5444,7 +5444,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>5.41651821136475</v>
+        <v>5.41651773452759</v>
       </c>
       <c r="H175" t="n">
         <v>5482</v>
@@ -5531,7 +5531,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H178" t="n">
         <v>3026</v>
@@ -5560,7 +5560,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G179" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>5.30483722686768</v>
+        <v>5.30483675003052</v>
       </c>
       <c r="H180" t="n">
         <v>5941</v>
@@ -5879,7 +5879,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>5.47235870361328</v>
+        <v>5.47235822677612</v>
       </c>
       <c r="H190" t="n">
         <v>7694</v>
@@ -5908,7 +5908,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>5.49097156524658</v>
+        <v>5.49097204208374</v>
       </c>
       <c r="H191" t="n">
         <v>7118</v>
@@ -6024,7 +6024,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G195" t="n">
-        <v>5.41651821136475</v>
+        <v>5.41651773452759</v>
       </c>
       <c r="H195" t="n">
         <v>9390</v>
@@ -24169,7 +24169,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="D821" t="n">
-        <v>3.4300000667572</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="E821" t="n">
         <v>3.36999988555908</v>
@@ -24184,6 +24184,35 @@
         <v>10513</v>
       </c>
       <c r="I821" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="s">
+        <v>9</v>
+      </c>
+      <c r="B822" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C822" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="D822" t="n">
+        <v>3.54999995231628</v>
+      </c>
+      <c r="E822" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="F822" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="G822" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="H822" t="n">
+        <v>21510</v>
+      </c>
+      <c r="I822" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SBC.MI.xlsx
+++ b/data/SBC.MI.xlsx
@@ -24216,6 +24216,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="823">
+      <c r="A823" t="s">
+        <v>9</v>
+      </c>
+      <c r="B823" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C823" t="n">
+        <v>3.5699999332428</v>
+      </c>
+      <c r="D823" t="n">
+        <v>3.5699999332428</v>
+      </c>
+      <c r="E823" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="F823" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G823" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H823" t="n">
+        <v>2610</v>
+      </c>
+      <c r="I823" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
